--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N21_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.10101833811624</v>
+        <v>3.266415479943888</v>
       </c>
       <c r="D2" t="n">
-        <v>8.254106515060371</v>
+        <v>1.34129230869731</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
